--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Bàsquet Girona.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Bàsquet Girona.xlsx
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>42.7206</v>
+        <v>66.48090000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>48.967</v>
+        <v>66.905</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.2464</v>
+        <v>-0.4240000000000007</v>
       </c>
       <c r="G2" t="n">
-        <v>11.409</v>
+        <v>12.9375</v>
       </c>
       <c r="H2" t="n">
-        <v>18.8424</v>
+        <v>19.991</v>
       </c>
       <c r="I2" t="n">
-        <v>-7.4328</v>
+        <v>-7.0531</v>
       </c>
       <c r="J2" t="n">
-        <v>45.6881</v>
+        <v>52.2759</v>
       </c>
       <c r="K2" t="n">
-        <v>27.2972</v>
+        <v>31.5875</v>
       </c>
       <c r="L2" t="n">
-        <v>18.3906</v>
+        <v>20.6883</v>
       </c>
       <c r="M2" t="n">
-        <v>-34.2788</v>
+        <v>-39.3382</v>
       </c>
       <c r="N2" t="n">
-        <v>-8.4556</v>
+        <v>-11.5969</v>
       </c>
       <c r="O2" t="n">
-        <v>-25.8235</v>
+        <v>-27.7418</v>
       </c>
       <c r="P2" t="n">
-        <v>-4.5365</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-47.635</v>
+        <v>-54.8595</v>
       </c>
       <c r="R2" t="n">
-        <v>43.0982</v>
+        <v>53.266</v>
       </c>
       <c r="S2" t="n">
-        <v>29.7746</v>
+        <v>46.8942</v>
       </c>
       <c r="T2" t="n">
-        <v>20.3186</v>
+        <v>35.1967</v>
       </c>
       <c r="U2" t="n">
-        <v>9.4558</v>
+        <v>11.6977</v>
       </c>
       <c r="V2" t="n">
-        <v>6.0738</v>
+        <v>8.242600000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>30.5954</v>
+        <v>34.2916</v>
       </c>
       <c r="X2" t="n">
-        <v>-24.5215</v>
+        <v>-26.0493</v>
       </c>
     </row>
     <row r="3">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>20.5049</v>
+        <v>16.1814</v>
       </c>
       <c r="E3" t="n">
-        <v>16.7889</v>
+        <v>17.0481</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7165</v>
+        <v>-0.8667999999999991</v>
       </c>
       <c r="G3" t="n">
-        <v>13.4809</v>
+        <v>9.154500000000002</v>
       </c>
       <c r="H3" t="n">
-        <v>8.0791</v>
+        <v>2.877</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4018</v>
+        <v>6.2776</v>
       </c>
       <c r="J3" t="n">
-        <v>20.6961</v>
+        <v>17.8677</v>
       </c>
       <c r="K3" t="n">
-        <v>15.7328</v>
+        <v>11.6487</v>
       </c>
       <c r="L3" t="n">
-        <v>4.9632</v>
+        <v>6.2183</v>
       </c>
       <c r="M3" t="n">
-        <v>-7.2153</v>
+        <v>-8.713100000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.6539</v>
+        <v>-8.771599999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4387000000000003</v>
+        <v>0.05889999999999974</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.9393</v>
+        <v>-7.0567</v>
       </c>
       <c r="Q3" t="n">
-        <v>-33.3446</v>
+        <v>-36.1937</v>
       </c>
       <c r="R3" t="n">
-        <v>25.4051</v>
+        <v>29.1368</v>
       </c>
       <c r="S3" t="n">
-        <v>21.1852</v>
+        <v>25.1299</v>
       </c>
       <c r="T3" t="n">
-        <v>18.9272</v>
+        <v>22.3124</v>
       </c>
       <c r="U3" t="n">
-        <v>2.2581</v>
+        <v>2.8177</v>
       </c>
       <c r="V3" t="n">
-        <v>-6.2215</v>
+        <v>-11.0465</v>
       </c>
       <c r="W3" t="n">
-        <v>10.51</v>
+        <v>13.0619</v>
       </c>
       <c r="X3" t="n">
-        <v>-16.7314</v>
+        <v>-24.1082</v>
       </c>
     </row>
     <row r="4">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>17.0793</v>
+        <v>11.6204</v>
       </c>
       <c r="E4" t="n">
-        <v>17.6053</v>
+        <v>12.9109</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.526099999999999</v>
+        <v>-1.2909</v>
       </c>
       <c r="G4" t="n">
-        <v>-13.289</v>
+        <v>-16.9793</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1936</v>
+        <v>-1.8884</v>
       </c>
       <c r="I4" t="n">
-        <v>-15.4826</v>
+        <v>-15.0912</v>
       </c>
       <c r="J4" t="n">
-        <v>20.8897</v>
+        <v>20.7081</v>
       </c>
       <c r="K4" t="n">
-        <v>13.8331</v>
+        <v>12.8983</v>
       </c>
       <c r="L4" t="n">
-        <v>7.0566</v>
+        <v>7.809799999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-34.1787</v>
+        <v>-37.6878</v>
       </c>
       <c r="N4" t="n">
-        <v>-11.6397</v>
+        <v>-14.7867</v>
       </c>
       <c r="O4" t="n">
-        <v>-22.5392</v>
+        <v>-22.9006</v>
       </c>
       <c r="P4" t="n">
-        <v>24.9515</v>
+        <v>24.3566</v>
       </c>
       <c r="Q4" t="n">
-        <v>-22.2295</v>
+        <v>-30.5025</v>
       </c>
       <c r="R4" t="n">
-        <v>47.1816</v>
+        <v>54.8593</v>
       </c>
       <c r="S4" t="n">
-        <v>10.1924</v>
+        <v>12.9926</v>
       </c>
       <c r="T4" t="n">
-        <v>4.579800000000001</v>
+        <v>8.4262</v>
       </c>
       <c r="U4" t="n">
-        <v>5.6127</v>
+        <v>4.5669</v>
       </c>
       <c r="V4" t="n">
-        <v>-4.7754</v>
+        <v>-8.749600000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>14.3662</v>
+        <v>14.2794</v>
       </c>
       <c r="X4" t="n">
-        <v>-19.1414</v>
+        <v>-23.0287</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. HUGHES</t>
+          <t>E. SANMARTIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>5.112900000000002</v>
+        <v>1.1123</v>
       </c>
       <c r="E5" t="n">
-        <v>7.5151</v>
+        <v>-0.1259</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.4023</v>
+        <v>1.2382</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.7118</v>
+        <v>1.1678</v>
       </c>
       <c r="H5" t="n">
-        <v>-6.653</v>
+        <v>-0.3191</v>
       </c>
       <c r="I5" t="n">
-        <v>4.9414</v>
+        <v>1.4868</v>
       </c>
       <c r="J5" t="n">
-        <v>20.6393</v>
+        <v>0.2924</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6578</v>
+        <v>0.0689</v>
       </c>
       <c r="L5" t="n">
-        <v>16.9816</v>
+        <v>0.2234</v>
       </c>
       <c r="M5" t="n">
-        <v>-22.3513</v>
+        <v>0.8754000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-10.3111</v>
+        <v>-0.3881</v>
       </c>
       <c r="O5" t="n">
-        <v>-12.0406</v>
+        <v>1.2634</v>
       </c>
       <c r="P5" t="n">
-        <v>5.444</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-33.1176</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>38.5616</v>
+        <v>0.2276</v>
       </c>
       <c r="S5" t="n">
-        <v>-5.239100000000001</v>
+        <v>-0.1253</v>
       </c>
       <c r="T5" t="n">
-        <v>-4.463699999999999</v>
+        <v>-0.4182</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7758</v>
+        <v>0.2929</v>
       </c>
       <c r="V5" t="n">
-        <v>6.62</v>
+        <v>-0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>24.4568</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-17.8369</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9252</v>
+        <v>-0.0613999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1473</v>
+        <v>-6.0596</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7779</v>
+        <v>5.998100000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1533</v>
+        <v>-5.2366</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7317</v>
+        <v>-2.2702</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5784</v>
+        <v>-2.9663</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3845</v>
+        <v>-4.6049</v>
       </c>
       <c r="K6" t="n">
-        <v>1.198</v>
+        <v>-1.9227</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1866</v>
+        <v>-2.6821</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2312</v>
+        <v>-0.6315999999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5337</v>
+        <v>-0.3472999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7649</v>
+        <v>-0.2840999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6805</v>
+        <v>-0.9104999999999998</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-8.194800000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>7.2842</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1866</v>
+        <v>3.8577</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6079</v>
+        <v>2.6828</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4213</v>
+        <v>1.175</v>
       </c>
       <c r="V6" t="n">
-        <v>1.639</v>
+        <v>2.2278</v>
       </c>
       <c r="W6" t="n">
-        <v>1.639</v>
+        <v>4.0573</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.8294</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. SANMARTIN</t>
+          <t>M. HUGHES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0994</v>
+        <v>-1.427600000000003</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1242</v>
+        <v>2.170199999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2236</v>
+        <v>-3.5977</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1574</v>
+        <v>-9.1196</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3248</v>
+        <v>-10.646</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4821</v>
+        <v>1.526099999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2932</v>
+        <v>20.1224</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0693</v>
+        <v>4.770200000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2239</v>
+        <v>15.3521</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8641</v>
+        <v>-29.2419</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3941</v>
+        <v>-15.4159</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2582</v>
+        <v>-13.8261</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>4.5528</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-43.7054</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>48.2581</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.124</v>
+        <v>-3.1787</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4174</v>
+        <v>-2.9752</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2934</v>
+        <v>-0.2032000000000004</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1607</v>
+        <v>6.3178</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>28.728</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>-22.4107</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>M. FJELLERUP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4793999999999996</v>
+        <v>-1.4954</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5517</v>
+        <v>-3.5535</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.031099999999999</v>
+        <v>2.0581</v>
       </c>
       <c r="G8" t="n">
-        <v>-7.8658</v>
+        <v>-2.8175</v>
       </c>
       <c r="H8" t="n">
-        <v>11.7333</v>
+        <v>-3.1087</v>
       </c>
       <c r="I8" t="n">
-        <v>-19.5989</v>
+        <v>0.2913000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>10.4145</v>
+        <v>-1.7343</v>
       </c>
       <c r="K8" t="n">
-        <v>16.1144</v>
+        <v>-2.5907</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.6998</v>
+        <v>0.8565</v>
       </c>
       <c r="M8" t="n">
-        <v>-18.2801</v>
+        <v>-1.0831</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.381</v>
+        <v>-0.5181</v>
       </c>
       <c r="O8" t="n">
-        <v>-13.899</v>
+        <v>-0.5650999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5878</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-25.1787</v>
+        <v>-4.097399999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>26.7666</v>
+        <v>3.8698</v>
       </c>
       <c r="S8" t="n">
-        <v>7.6751</v>
+        <v>-1.0449</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7930000000000003</v>
+        <v>-1.3058</v>
       </c>
       <c r="U8" t="n">
-        <v>6.8823</v>
+        <v>0.2607999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8768</v>
+        <v>2.5945</v>
       </c>
       <c r="W8" t="n">
-        <v>15.523</v>
+        <v>3.5839</v>
       </c>
       <c r="X8" t="n">
-        <v>-17.3996</v>
+        <v>-0.9895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. HILDRETH</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.109</v>
+        <v>-4.638800000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7538000000000001</v>
+        <v>-5.2005</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3551999999999997</v>
+        <v>0.5616000000000003</v>
       </c>
       <c r="G9" t="n">
-        <v>3.0861</v>
+        <v>-13.2547</v>
       </c>
       <c r="H9" t="n">
-        <v>4.267</v>
+        <v>8.612799999999998</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1807</v>
+        <v>-21.8673</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9563</v>
+        <v>5.113</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4521</v>
+        <v>14.57</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.496</v>
+        <v>-9.457000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1299</v>
+        <v>-18.3675</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8147000000000001</v>
+        <v>-5.957</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6849</v>
+        <v>-12.4102</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.3098</v>
+        <v>3.1868</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.805</v>
+        <v>-26.6332</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4951</v>
+        <v>29.82</v>
       </c>
       <c r="S9" t="n">
-        <v>2.0752</v>
+        <v>8.2468</v>
       </c>
       <c r="T9" t="n">
-        <v>2.0023</v>
+        <v>0.5640000000000002</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07289999999999994</v>
+        <v>7.682600000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.9605</v>
+        <v>-2.8178</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>15.7559</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.0532</v>
+        <v>-18.5734</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. FJELLERUP</t>
+          <t>K. BRUNOT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4753</v>
+        <v>-5.1107</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.469</v>
+        <v>-3.4661</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9936</v>
+        <v>-1.6446</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.8052</v>
+        <v>-3.2719</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.0773</v>
+        <v>-2.5809</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2721</v>
+        <v>-0.6910000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.681999999999999</v>
+        <v>-1.5114</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.5402</v>
+        <v>-0.06570000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8582</v>
+        <v>-1.4457</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1233</v>
+        <v>-1.7605</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5371</v>
+        <v>-2.5152</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5861999999999998</v>
+        <v>0.7548</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>1.665334536937735e-16</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.083</v>
+        <v>-3.6422</v>
       </c>
       <c r="R10" t="n">
-        <v>3.8562</v>
+        <v>3.6422</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0398</v>
+        <v>-1.2943</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3035</v>
+        <v>0.4401999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2637</v>
+        <v>-1.7344</v>
       </c>
       <c r="V10" t="n">
-        <v>2.5966</v>
+        <v>-0.5448</v>
       </c>
       <c r="W10" t="n">
-        <v>3.5994</v>
+        <v>1.2472</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0028</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. BRUNOT</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2548</v>
+        <v>-6.9907</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1531</v>
+        <v>-4.1101</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1017</v>
+        <v>-2.880599999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.5666</v>
+        <v>-1.6009</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.6122</v>
+        <v>1.0506</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9540999999999998</v>
+        <v>-2.6514</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.488</v>
+        <v>-0.04559999999999986</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.059</v>
+        <v>1.296</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4288</v>
+        <v>-1.3418</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0785</v>
+        <v>-1.5553</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.5531</v>
+        <v>-0.2455</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4746000000000001</v>
+        <v>-1.3099</v>
       </c>
       <c r="P11" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.6294</v>
+        <v>-4.7803</v>
       </c>
       <c r="R11" t="n">
-        <v>3.6294</v>
+        <v>2.7315</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.142</v>
+        <v>0.9454999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7108000000000001</v>
+        <v>0.1711000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.8528</v>
+        <v>0.7742999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5463</v>
+        <v>-4.2865</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2534</v>
+        <v>0.5447</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7997</v>
+        <v>-4.8313</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>C. HILDRETH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.0194</v>
+        <v>-7.6706</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0615</v>
+        <v>-3.8608</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.958</v>
+        <v>-3.81</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.6135</v>
+        <v>-0.007800000000000085</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0388</v>
+        <v>2.6606</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.6523</v>
+        <v>-2.6685</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.01060000000000005</v>
+        <v>4.9894</v>
       </c>
       <c r="K12" t="n">
-        <v>1.309</v>
+        <v>4.9917</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3196</v>
+        <v>-0.002099999999999935</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6029</v>
+        <v>-4.9973</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2702000000000001</v>
+        <v>-2.3311</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3327</v>
+        <v>-2.6662</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.0415</v>
+        <v>-7.511900000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.763500000000001</v>
+        <v>-18.4382</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7219</v>
+        <v>10.9263</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9420000000000001</v>
+        <v>-2.2209</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1665</v>
+        <v>-1.006</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7758999999999998</v>
+        <v>-1.215</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.3065</v>
+        <v>2.07</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5463</v>
+        <v>10.5941</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.8529</v>
+        <v>-8.524099999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.3751</v>
+        <v>-17.2991</v>
       </c>
       <c r="E13" t="n">
-        <v>-18.4819</v>
+        <v>-7.063000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>5.1068</v>
+        <v>-10.2361</v>
       </c>
       <c r="G13" t="n">
-        <v>1.241299999999999</v>
+        <v>-1.532599999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>10.0779</v>
+        <v>-0.2937000000000007</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.836499999999999</v>
+        <v>-1.2387</v>
       </c>
       <c r="J13" t="n">
-        <v>23.6483</v>
+        <v>12.0674</v>
       </c>
       <c r="K13" t="n">
-        <v>19.5947</v>
+        <v>9.2752</v>
       </c>
       <c r="L13" t="n">
-        <v>4.0536</v>
+        <v>2.7925</v>
       </c>
       <c r="M13" t="n">
-        <v>-22.4071</v>
+        <v>-13.6004</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.5169</v>
+        <v>-9.5692</v>
       </c>
       <c r="O13" t="n">
-        <v>-12.89</v>
+        <v>-4.0316</v>
       </c>
       <c r="P13" t="n">
-        <v>2.0415</v>
+        <v>22.7633</v>
       </c>
       <c r="Q13" t="n">
-        <v>-48.7692</v>
+        <v>-22.7632</v>
       </c>
       <c r="R13" t="n">
-        <v>50.8108</v>
+        <v>45.5265</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.2125</v>
+        <v>-4.2101</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.9677</v>
+        <v>-5.3986</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7554000000000001</v>
+        <v>1.1888</v>
       </c>
       <c r="V13" t="n">
-        <v>-13.4457</v>
+        <v>-34.3193</v>
       </c>
       <c r="W13" t="n">
-        <v>10.6065</v>
+        <v>9.0313</v>
       </c>
       <c r="X13" t="n">
-        <v>-24.052</v>
+        <v>-43.3507</v>
       </c>
     </row>
     <row r="14">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.0851</v>
+        <v>-23.174</v>
       </c>
       <c r="E14" t="n">
-        <v>-12.7896</v>
+        <v>-24.6542</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.295199999999999</v>
+        <v>1.4802</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.649000000000001</v>
+        <v>-16.9517</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.3181</v>
+        <v>-9.417300000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.331</v>
+        <v>-7.5343</v>
       </c>
       <c r="J14" t="n">
-        <v>6.146400000000001</v>
+        <v>0.08489999999999857</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01919999999999999</v>
+        <v>-1.3166</v>
       </c>
       <c r="L14" t="n">
-        <v>6.1273</v>
+        <v>1.4019</v>
       </c>
       <c r="M14" t="n">
-        <v>-15.7954</v>
+        <v>-17.0365</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.3372</v>
+        <v>-8.100399999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.458600000000001</v>
+        <v>-8.936</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9074000000000003</v>
+        <v>2.048800000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-28.1273</v>
+        <v>-33.9169</v>
       </c>
       <c r="R14" t="n">
-        <v>29.0348</v>
+        <v>35.9662</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.9474</v>
+        <v>-5.607699999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.203</v>
+        <v>-7.2502</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2551999999999998</v>
+        <v>1.6427</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6040999999999999</v>
+        <v>-2.6636</v>
       </c>
       <c r="W14" t="n">
-        <v>15.3941</v>
+        <v>16.4285</v>
       </c>
       <c r="X14" t="n">
-        <v>-14.7898</v>
+        <v>-19.0922</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. FERRANDO</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>-18.4809</v>
+        <v>-23.4772</v>
       </c>
       <c r="E15" t="n">
-        <v>-17.2906</v>
+        <v>-38.5299</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1901</v>
+        <v>15.0528</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.8499</v>
+        <v>-13.7593</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5722</v>
+        <v>3.474900000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-5.4222</v>
+        <v>-17.2344</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3804</v>
+        <v>7.546</v>
       </c>
       <c r="K15" t="n">
-        <v>5.4783</v>
+        <v>11.9302</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.098</v>
+        <v>-4.384600000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.2306</v>
+        <v>-21.305</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.9063</v>
+        <v>-8.4552</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3239</v>
+        <v>-12.8499</v>
       </c>
       <c r="P15" t="n">
-        <v>-10.4345</v>
+        <v>1.821099999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-22.0031</v>
+        <v>-58.7288</v>
       </c>
       <c r="R15" t="n">
-        <v>11.5684</v>
+        <v>60.5502</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.0037</v>
+        <v>4.675599999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.521</v>
+        <v>0.7524</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.4823</v>
+        <v>3.9233</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1929000000000001</v>
+        <v>-16.2148</v>
       </c>
       <c r="W15" t="n">
-        <v>4.8529</v>
+        <v>11.901</v>
       </c>
       <c r="X15" t="n">
-        <v>-5.0456</v>
+        <v>-28.1156</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>G. FERRANDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>-21.5235</v>
+        <v>-23.833</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.086</v>
+        <v>-22.168</v>
       </c>
       <c r="F16" t="n">
-        <v>-15.4374</v>
+        <v>-1.665</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.5238</v>
+        <v>-5.7651</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1790999999999999</v>
+        <v>2.0479</v>
       </c>
       <c r="I16" t="n">
-        <v>-5.344499999999999</v>
+        <v>-7.8132</v>
       </c>
       <c r="J16" t="n">
-        <v>6.629000000000001</v>
+        <v>-0.1543999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>9.1051</v>
+        <v>5.6011</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.476</v>
+        <v>-5.7551</v>
       </c>
       <c r="M16" t="n">
-        <v>-12.1528</v>
+        <v>-5.6106</v>
       </c>
       <c r="N16" t="n">
-        <v>-9.2844</v>
+        <v>-3.5529</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.8685</v>
+        <v>-2.0577</v>
       </c>
       <c r="P16" t="n">
-        <v>19.5077</v>
+        <v>-11.6094</v>
       </c>
       <c r="Q16" t="n">
-        <v>-15.4246</v>
+        <v>-24.5846</v>
       </c>
       <c r="R16" t="n">
-        <v>34.9323</v>
+        <v>12.975</v>
       </c>
       <c r="S16" t="n">
-        <v>-5.4643</v>
+        <v>-6.1606</v>
       </c>
       <c r="T16" t="n">
-        <v>-5.6464</v>
+        <v>-2.2607</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1816000000000002</v>
+        <v>-3.9002</v>
       </c>
       <c r="V16" t="n">
-        <v>-30.0423</v>
+        <v>-0.2982000000000002</v>
       </c>
       <c r="W16" t="n">
-        <v>8.355700000000001</v>
+        <v>4.8313</v>
       </c>
       <c r="X16" t="n">
-        <v>-38.398</v>
+        <v>-5.129300000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>-32.101</v>
+        <v>-38.0178</v>
       </c>
       <c r="E17" t="n">
-        <v>-11.4099</v>
+        <v>-21.1358</v>
       </c>
       <c r="F17" t="n">
-        <v>-20.6914</v>
+        <v>-16.8821</v>
       </c>
       <c r="G17" t="n">
-        <v>8.565099999999997</v>
+        <v>16.3227</v>
       </c>
       <c r="H17" t="n">
-        <v>-6.9838</v>
+        <v>-10.1091</v>
       </c>
       <c r="I17" t="n">
-        <v>15.549</v>
+        <v>26.4318</v>
       </c>
       <c r="J17" t="n">
-        <v>48.6386</v>
+        <v>59.7766</v>
       </c>
       <c r="K17" t="n">
-        <v>9.1433</v>
+        <v>8.543999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>39.4951</v>
+        <v>51.2318</v>
       </c>
       <c r="M17" t="n">
-        <v>-40.0739</v>
+        <v>-43.4533</v>
       </c>
       <c r="N17" t="n">
-        <v>-16.1276</v>
+        <v>-18.6528</v>
       </c>
       <c r="O17" t="n">
-        <v>-23.9466</v>
+        <v>-24.8003</v>
       </c>
       <c r="P17" t="n">
-        <v>-22.2297</v>
+        <v>-36.4213</v>
       </c>
       <c r="Q17" t="n">
-        <v>-71.67919999999999</v>
+        <v>-97.65390000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>49.4496</v>
+        <v>61.2331</v>
       </c>
       <c r="S17" t="n">
-        <v>-23.2827</v>
+        <v>-26.7107</v>
       </c>
       <c r="T17" t="n">
-        <v>-15.751</v>
+        <v>-15.7432</v>
       </c>
       <c r="U17" t="n">
-        <v>-7.5319</v>
+        <v>-10.967</v>
       </c>
       <c r="V17" t="n">
-        <v>4.846400000000001</v>
+        <v>8.790899999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>27.3816</v>
+        <v>32.4848</v>
       </c>
       <c r="X17" t="n">
-        <v>-22.5352</v>
+        <v>-23.6941</v>
       </c>
     </row>
     <row r="18">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>-48.8573</v>
+        <v>-46.2968</v>
       </c>
       <c r="E18" t="n">
-        <v>-23.824</v>
+        <v>-17.0353</v>
       </c>
       <c r="F18" t="n">
-        <v>-25.0335</v>
+        <v>-29.2612</v>
       </c>
       <c r="G18" t="n">
-        <v>10.4078</v>
+        <v>22.3085</v>
       </c>
       <c r="H18" t="n">
-        <v>-10.063</v>
+        <v>-12.9184</v>
       </c>
       <c r="I18" t="n">
-        <v>20.4706</v>
+        <v>35.2265</v>
       </c>
       <c r="J18" t="n">
-        <v>34.2437</v>
+        <v>48.4535</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0472999999999999</v>
+        <v>0.02920000000000034</v>
       </c>
       <c r="L18" t="n">
-        <v>34.2914</v>
+        <v>48.4242</v>
       </c>
       <c r="M18" t="n">
-        <v>-23.8363</v>
+        <v>-26.1453</v>
       </c>
       <c r="N18" t="n">
-        <v>-10.0155</v>
+        <v>-12.9479</v>
       </c>
       <c r="O18" t="n">
-        <v>-13.8209</v>
+        <v>-13.1973</v>
       </c>
       <c r="P18" t="n">
-        <v>-19.2807</v>
+        <v>-21.1695</v>
       </c>
       <c r="Q18" t="n">
-        <v>-66.4619</v>
+        <v>-79.8986</v>
       </c>
       <c r="R18" t="n">
-        <v>47.1814</v>
+        <v>58.729</v>
       </c>
       <c r="S18" t="n">
-        <v>-16.922</v>
+        <v>-16.3784</v>
       </c>
       <c r="T18" t="n">
-        <v>-8.1564</v>
+        <v>-3.7241</v>
       </c>
       <c r="U18" t="n">
-        <v>-8.7654</v>
+        <v>-12.6538</v>
       </c>
       <c r="V18" t="n">
-        <v>-23.0622</v>
+        <v>-31.057</v>
       </c>
       <c r="W18" t="n">
-        <v>16.5509</v>
+        <v>18.1342</v>
       </c>
       <c r="X18" t="n">
-        <v>-39.6129</v>
+        <v>-49.1912</v>
       </c>
     </row>
     <row r="19">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D19" t="n">
-        <v>-75.3185</v>
+        <v>-104.0981</v>
       </c>
       <c r="E19" t="n">
-        <v>-8.868300000000005</v>
+        <v>-57.92849999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-66.45</v>
+        <v>-46.17</v>
       </c>
       <c r="G19" t="n">
-        <v>1.626299999999997</v>
+        <v>-28.406</v>
       </c>
       <c r="H19" t="n">
-        <v>24.3247</v>
+        <v>-12.83700000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-22.69700000000001</v>
+        <v>-15.5693</v>
       </c>
       <c r="J19" t="n">
-        <v>240.4675</v>
+        <v>241.2467</v>
       </c>
       <c r="K19" t="n">
-        <v>123.3578</v>
+        <v>111.3153</v>
       </c>
       <c r="L19" t="n">
-        <v>117.1099</v>
+        <v>129.9304</v>
       </c>
       <c r="M19" t="n">
-        <v>-238.8422</v>
+        <v>-269.652</v>
       </c>
       <c r="N19" t="n">
-        <v>-99.03530000000001</v>
+        <v>-124.1518</v>
       </c>
       <c r="O19" t="n">
-        <v>-139.808</v>
+        <v>-145.4997</v>
       </c>
       <c r="P19" t="n">
-        <v>-17.0126</v>
+        <v>-29.59200000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>-435.5199</v>
+        <v>-548.5932</v>
       </c>
       <c r="R19" t="n">
-        <v>418.5076</v>
+        <v>519.0018</v>
       </c>
       <c r="S19" t="n">
-        <v>4.280400000000007</v>
+        <v>35.8107</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5398000000000014</v>
+        <v>30.4638</v>
       </c>
       <c r="U19" t="n">
-        <v>4.820100000000002</v>
+        <v>5.349099999999996</v>
       </c>
       <c r="V19" t="n">
-        <v>-64.21090000000001</v>
+        <v>-81.9123</v>
       </c>
       <c r="W19" t="n">
-        <v>186.7239</v>
+        <v>218.9551</v>
       </c>
       <c r="X19" t="n">
-        <v>-250.9336</v>
+        <v>-300.8675</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Bàsquet Girona.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Bàsquet Girona.xlsx
@@ -565,13 +565,13 @@
         <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>66.48090000000001</v>
+        <v>41.3736</v>
       </c>
       <c r="E2" t="n">
-        <v>66.905</v>
+        <v>46.1988</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4240000000000007</v>
+        <v>-4.8249</v>
       </c>
       <c r="G2" t="n">
         <v>12.9375</v>
@@ -610,13 +610,13 @@
         <v>53.266</v>
       </c>
       <c r="S2" t="n">
-        <v>46.8942</v>
+        <v>21.7868</v>
       </c>
       <c r="T2" t="n">
-        <v>35.1967</v>
+        <v>14.4901</v>
       </c>
       <c r="U2" t="n">
-        <v>11.6977</v>
+        <v>7.2969</v>
       </c>
       <c r="V2" t="n">
         <v>8.242600000000001</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>S. MARTINEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>16.1814</v>
+        <v>11.2546</v>
       </c>
       <c r="E3" t="n">
-        <v>17.0481</v>
+        <v>12.5704</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8667999999999991</v>
+        <v>-1.316299999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>9.154500000000002</v>
+        <v>-16.9793</v>
       </c>
       <c r="H3" t="n">
-        <v>2.877</v>
+        <v>-1.8884</v>
       </c>
       <c r="I3" t="n">
-        <v>6.2776</v>
+        <v>-15.0912</v>
       </c>
       <c r="J3" t="n">
-        <v>17.8677</v>
+        <v>20.7081</v>
       </c>
       <c r="K3" t="n">
-        <v>11.6487</v>
+        <v>12.8983</v>
       </c>
       <c r="L3" t="n">
-        <v>6.2183</v>
+        <v>7.809799999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-8.713100000000001</v>
+        <v>-37.6878</v>
       </c>
       <c r="N3" t="n">
-        <v>-8.771599999999999</v>
+        <v>-14.7867</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05889999999999974</v>
+        <v>-22.9006</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.0567</v>
+        <v>24.3566</v>
       </c>
       <c r="Q3" t="n">
-        <v>-36.1937</v>
+        <v>-30.5025</v>
       </c>
       <c r="R3" t="n">
-        <v>29.1368</v>
+        <v>54.8593</v>
       </c>
       <c r="S3" t="n">
-        <v>25.1299</v>
+        <v>12.6271</v>
       </c>
       <c r="T3" t="n">
-        <v>22.3124</v>
+        <v>8.085599999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>2.8177</v>
+        <v>4.5413</v>
       </c>
       <c r="V3" t="n">
-        <v>-11.0465</v>
+        <v>-8.749600000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>13.0619</v>
+        <v>14.2794</v>
       </c>
       <c r="X3" t="n">
-        <v>-24.1082</v>
+        <v>-23.0287</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. MARTINEZ</t>
+          <t>M. HUGHES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>11.6204</v>
+        <v>8.787900000000002</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9109</v>
+        <v>8.671199999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2909</v>
+        <v>0.1166999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-16.9793</v>
+        <v>-9.1196</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.8884</v>
+        <v>-10.646</v>
       </c>
       <c r="I4" t="n">
-        <v>-15.0912</v>
+        <v>1.526099999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>20.7081</v>
+        <v>20.1224</v>
       </c>
       <c r="K4" t="n">
-        <v>12.8983</v>
+        <v>4.770200000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>7.809799999999999</v>
+        <v>15.3521</v>
       </c>
       <c r="M4" t="n">
-        <v>-37.6878</v>
+        <v>-29.2419</v>
       </c>
       <c r="N4" t="n">
-        <v>-14.7867</v>
+        <v>-15.4159</v>
       </c>
       <c r="O4" t="n">
-        <v>-22.9006</v>
+        <v>-13.8261</v>
       </c>
       <c r="P4" t="n">
-        <v>24.3566</v>
+        <v>4.5528</v>
       </c>
       <c r="Q4" t="n">
-        <v>-30.5025</v>
+        <v>-43.7054</v>
       </c>
       <c r="R4" t="n">
-        <v>54.8593</v>
+        <v>48.2581</v>
       </c>
       <c r="S4" t="n">
-        <v>12.9926</v>
+        <v>7.0374</v>
       </c>
       <c r="T4" t="n">
-        <v>8.4262</v>
+        <v>3.5262</v>
       </c>
       <c r="U4" t="n">
-        <v>4.5669</v>
+        <v>3.511</v>
       </c>
       <c r="V4" t="n">
-        <v>-8.749600000000001</v>
+        <v>6.3178</v>
       </c>
       <c r="W4" t="n">
-        <v>14.2794</v>
+        <v>28.728</v>
       </c>
       <c r="X4" t="n">
-        <v>-23.0287</v>
+        <v>-22.4107</v>
       </c>
     </row>
     <row r="5">
@@ -799,10 +799,10 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1123</v>
+        <v>1.5374</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1259</v>
+        <v>0.2992</v>
       </c>
       <c r="F5" t="n">
         <v>1.2382</v>
@@ -844,13 +844,13 @@
         <v>0.2276</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1253</v>
+        <v>0.2998</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4182</v>
+        <v>0.0068</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2929</v>
+        <v>0.293</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1578</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. KARNIK</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0613999999999999</v>
+        <v>0.787500000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-6.0596</v>
+        <v>1.9917</v>
       </c>
       <c r="F6" t="n">
-        <v>5.998100000000001</v>
+        <v>-1.2042</v>
       </c>
       <c r="G6" t="n">
-        <v>-5.2366</v>
+        <v>9.154500000000002</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.2702</v>
+        <v>2.877</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.9663</v>
+        <v>6.2776</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.6049</v>
+        <v>17.8677</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.9227</v>
+        <v>11.6487</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.6821</v>
+        <v>6.2183</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6315999999999998</v>
+        <v>-8.713100000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3472999999999999</v>
+        <v>-8.771599999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2840999999999999</v>
+        <v>0.05889999999999974</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9104999999999998</v>
+        <v>-7.0567</v>
       </c>
       <c r="Q6" t="n">
-        <v>-8.194800000000001</v>
+        <v>-36.1937</v>
       </c>
       <c r="R6" t="n">
-        <v>7.2842</v>
+        <v>29.1368</v>
       </c>
       <c r="S6" t="n">
-        <v>3.8577</v>
+        <v>9.736000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6828</v>
+        <v>7.2559</v>
       </c>
       <c r="U6" t="n">
-        <v>1.175</v>
+        <v>2.4804</v>
       </c>
       <c r="V6" t="n">
-        <v>2.2278</v>
+        <v>-11.0465</v>
       </c>
       <c r="W6" t="n">
-        <v>4.0573</v>
+        <v>13.0619</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8294</v>
+        <v>-24.1082</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. HUGHES</t>
+          <t>M. FJELLERUP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.427600000000003</v>
+        <v>-0.7686999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>2.170199999999999</v>
+        <v>-3.0797</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.5977</v>
+        <v>2.3112</v>
       </c>
       <c r="G7" t="n">
-        <v>-9.1196</v>
+        <v>-2.8175</v>
       </c>
       <c r="H7" t="n">
-        <v>-10.646</v>
+        <v>-3.1087</v>
       </c>
       <c r="I7" t="n">
-        <v>1.526099999999999</v>
+        <v>0.2913000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>20.1224</v>
+        <v>-1.7343</v>
       </c>
       <c r="K7" t="n">
-        <v>4.770200000000001</v>
+        <v>-2.5907</v>
       </c>
       <c r="L7" t="n">
-        <v>15.3521</v>
+        <v>0.8565</v>
       </c>
       <c r="M7" t="n">
-        <v>-29.2419</v>
+        <v>-1.0831</v>
       </c>
       <c r="N7" t="n">
-        <v>-15.4159</v>
+        <v>-0.5181</v>
       </c>
       <c r="O7" t="n">
-        <v>-13.8261</v>
+        <v>-0.5650999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>4.5528</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-43.7054</v>
+        <v>-4.097399999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>48.2581</v>
+        <v>3.8698</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.1787</v>
+        <v>-0.3181</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.9752</v>
+        <v>-0.8321000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2032000000000004</v>
+        <v>0.514</v>
       </c>
       <c r="V7" t="n">
-        <v>6.3178</v>
+        <v>2.5945</v>
       </c>
       <c r="W7" t="n">
-        <v>28.728</v>
+        <v>3.5839</v>
       </c>
       <c r="X7" t="n">
-        <v>-22.4107</v>
+        <v>-0.9895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. FJELLERUP</t>
+          <t>J. KARNIK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4954</v>
+        <v>-1.7816</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.5535</v>
+        <v>-7.1533</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0581</v>
+        <v>5.372</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.8175</v>
+        <v>-5.2366</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.1087</v>
+        <v>-2.2702</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2913000000000001</v>
+        <v>-2.9663</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.7343</v>
+        <v>-4.6049</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.5907</v>
+        <v>-1.9227</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8565</v>
+        <v>-2.6821</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0831</v>
+        <v>-0.6315999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5181</v>
+        <v>-0.3472999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5650999999999999</v>
+        <v>-0.2840999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2276</v>
+        <v>-0.9104999999999998</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.097399999999999</v>
+        <v>-8.194800000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>3.8698</v>
+        <v>7.2842</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0449</v>
+        <v>2.1378</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3058</v>
+        <v>1.5891</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2607999999999999</v>
+        <v>0.5488000000000002</v>
       </c>
       <c r="V8" t="n">
-        <v>2.5945</v>
+        <v>2.2278</v>
       </c>
       <c r="W8" t="n">
-        <v>3.5839</v>
+        <v>4.0573</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9895</v>
+        <v>-1.8294</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>K. BRUNOT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.638800000000001</v>
+        <v>-4.6913</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.2005</v>
+        <v>-3.6123</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5616000000000003</v>
+        <v>-1.079</v>
       </c>
       <c r="G9" t="n">
-        <v>-13.2547</v>
+        <v>-3.2719</v>
       </c>
       <c r="H9" t="n">
-        <v>8.612799999999998</v>
+        <v>-2.5809</v>
       </c>
       <c r="I9" t="n">
-        <v>-21.8673</v>
+        <v>-0.6910000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>5.113</v>
+        <v>-1.5114</v>
       </c>
       <c r="K9" t="n">
-        <v>14.57</v>
+        <v>-0.06570000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.457000000000001</v>
+        <v>-1.4457</v>
       </c>
       <c r="M9" t="n">
-        <v>-18.3675</v>
+        <v>-1.7605</v>
       </c>
       <c r="N9" t="n">
-        <v>-5.957</v>
+        <v>-2.5152</v>
       </c>
       <c r="O9" t="n">
-        <v>-12.4102</v>
+        <v>0.7548</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1868</v>
+        <v>1.665334536937735e-16</v>
       </c>
       <c r="Q9" t="n">
-        <v>-26.6332</v>
+        <v>-3.6422</v>
       </c>
       <c r="R9" t="n">
-        <v>29.82</v>
+        <v>3.6422</v>
       </c>
       <c r="S9" t="n">
-        <v>8.2468</v>
+        <v>-0.8749</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5640000000000002</v>
+        <v>0.2939000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>7.682600000000001</v>
+        <v>-1.1687</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.8178</v>
+        <v>-0.5448</v>
       </c>
       <c r="W9" t="n">
-        <v>15.7559</v>
+        <v>1.2472</v>
       </c>
       <c r="X9" t="n">
-        <v>-18.5734</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. BRUNOT</t>
+          <t>C. HILDRETH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.1107</v>
+        <v>-4.9205</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4661</v>
+        <v>-2.0211</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6446</v>
+        <v>-2.8991</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2719</v>
+        <v>-0.007800000000000085</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5809</v>
+        <v>2.6606</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6910000000000001</v>
+        <v>-2.6685</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5114</v>
+        <v>4.9894</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.06570000000000001</v>
+        <v>4.9917</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4457</v>
+        <v>-0.002099999999999935</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7605</v>
+        <v>-4.9973</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.5152</v>
+        <v>-2.3311</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7548</v>
+        <v>-2.6662</v>
       </c>
       <c r="P10" t="n">
-        <v>1.665334536937735e-16</v>
+        <v>-7.511900000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6422</v>
+        <v>-18.4382</v>
       </c>
       <c r="R10" t="n">
-        <v>3.6422</v>
+        <v>10.9263</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2943</v>
+        <v>0.5294</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4401999999999999</v>
+        <v>0.8334999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.7344</v>
+        <v>-0.3042</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5448</v>
+        <v>2.07</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2472</v>
+        <v>10.5941</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.792</v>
+        <v>-8.524099999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.9907</v>
+        <v>-6.6534</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1101</v>
+        <v>-5.151200000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.880599999999999</v>
+        <v>-1.5021</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6009</v>
+        <v>-13.2547</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0506</v>
+        <v>8.612799999999998</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6514</v>
+        <v>-21.8673</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.04559999999999986</v>
+        <v>5.113</v>
       </c>
       <c r="K11" t="n">
-        <v>1.296</v>
+        <v>14.57</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3418</v>
+        <v>-9.457000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5553</v>
+        <v>-18.3675</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2455</v>
+        <v>-5.957</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3099</v>
+        <v>-12.4102</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0487</v>
+        <v>3.1868</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.7803</v>
+        <v>-26.6332</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7315</v>
+        <v>29.82</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9454999999999999</v>
+        <v>6.2323</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1711000000000001</v>
+        <v>0.6132</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7742999999999999</v>
+        <v>5.6191</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.2865</v>
+        <v>-2.8178</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5447</v>
+        <v>15.7559</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.8313</v>
+        <v>-18.5734</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. HILDRETH</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.6706</v>
+        <v>-7.147699999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8608</v>
+        <v>-4.109999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.81</v>
+        <v>-3.0375</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.007800000000000085</v>
+        <v>-1.6009</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6606</v>
+        <v>1.0506</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.6685</v>
+        <v>-2.6514</v>
       </c>
       <c r="J12" t="n">
-        <v>4.9894</v>
+        <v>-0.04559999999999986</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9917</v>
+        <v>1.296</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.002099999999999935</v>
+        <v>-1.3418</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.9973</v>
+        <v>-1.5553</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.3311</v>
+        <v>-0.2455</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.6662</v>
+        <v>-1.3099</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.511900000000001</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q12" t="n">
-        <v>-18.4382</v>
+        <v>-4.7803</v>
       </c>
       <c r="R12" t="n">
-        <v>10.9263</v>
+        <v>2.7315</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2209</v>
+        <v>0.7886000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.006</v>
+        <v>0.171</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.215</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>2.07</v>
+        <v>-4.2865</v>
       </c>
       <c r="W12" t="n">
-        <v>10.5941</v>
+        <v>0.5447</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.524099999999999</v>
+        <v>-4.8313</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>33</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.2991</v>
+        <v>-10.7596</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.063000000000001</v>
+        <v>-2.233899999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.2361</v>
+        <v>-8.526100000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-1.532599999999999</v>
@@ -1468,13 +1468,13 @@
         <v>45.5265</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.2101</v>
+        <v>2.329</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.3986</v>
+        <v>-0.5697</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1888</v>
+        <v>2.8992</v>
       </c>
       <c r="V13" t="n">
         <v>-34.3193</v>
@@ -1501,13 +1501,13 @@
         <v>32</v>
       </c>
       <c r="D14" t="n">
-        <v>-23.174</v>
+        <v>-11.9344</v>
       </c>
       <c r="E14" t="n">
-        <v>-24.6542</v>
+        <v>-15.6798</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4802</v>
+        <v>3.745</v>
       </c>
       <c r="G14" t="n">
         <v>-16.9517</v>
@@ -1546,13 +1546,13 @@
         <v>35.9662</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.607699999999999</v>
+        <v>5.6325</v>
       </c>
       <c r="T14" t="n">
-        <v>-7.2502</v>
+        <v>1.7241</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6427</v>
+        <v>3.9082</v>
       </c>
       <c r="V14" t="n">
         <v>-2.6636</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>O. LIVINGSTON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>-23.4772</v>
+        <v>-13.3838</v>
       </c>
       <c r="E15" t="n">
-        <v>-38.5299</v>
+        <v>-5.744499999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>15.0528</v>
+        <v>-7.639099999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-13.7593</v>
+        <v>16.3227</v>
       </c>
       <c r="H15" t="n">
-        <v>3.474900000000001</v>
+        <v>-10.1091</v>
       </c>
       <c r="I15" t="n">
-        <v>-17.2344</v>
+        <v>26.4318</v>
       </c>
       <c r="J15" t="n">
-        <v>7.546</v>
+        <v>59.7766</v>
       </c>
       <c r="K15" t="n">
-        <v>11.9302</v>
+        <v>8.543999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.384600000000001</v>
+        <v>51.2318</v>
       </c>
       <c r="M15" t="n">
-        <v>-21.305</v>
+        <v>-43.4533</v>
       </c>
       <c r="N15" t="n">
-        <v>-8.4552</v>
+        <v>-18.6528</v>
       </c>
       <c r="O15" t="n">
-        <v>-12.8499</v>
+        <v>-24.8003</v>
       </c>
       <c r="P15" t="n">
-        <v>1.821099999999999</v>
+        <v>-36.4213</v>
       </c>
       <c r="Q15" t="n">
-        <v>-58.7288</v>
+        <v>-97.65390000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>60.5502</v>
+        <v>61.2331</v>
       </c>
       <c r="S15" t="n">
-        <v>4.675599999999999</v>
+        <v>-2.0762</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7524</v>
+        <v>-0.3514</v>
       </c>
       <c r="U15" t="n">
-        <v>3.9233</v>
+        <v>-1.7245</v>
       </c>
       <c r="V15" t="n">
-        <v>-16.2148</v>
+        <v>8.790899999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>11.901</v>
+        <v>32.4848</v>
       </c>
       <c r="X15" t="n">
-        <v>-28.1156</v>
+        <v>-23.6941</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. FERRANDO</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>-23.833</v>
+        <v>-17.2652</v>
       </c>
       <c r="E16" t="n">
-        <v>-22.168</v>
+        <v>-31.2692</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.665</v>
+        <v>14.0037</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.7651</v>
+        <v>-13.7593</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0479</v>
+        <v>3.474900000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-7.8132</v>
+        <v>-17.2344</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1543999999999999</v>
+        <v>7.546</v>
       </c>
       <c r="K16" t="n">
-        <v>5.6011</v>
+        <v>11.9302</v>
       </c>
       <c r="L16" t="n">
-        <v>-5.7551</v>
+        <v>-4.384600000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.6106</v>
+        <v>-21.305</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.5529</v>
+        <v>-8.4552</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.0577</v>
+        <v>-12.8499</v>
       </c>
       <c r="P16" t="n">
-        <v>-11.6094</v>
+        <v>1.821099999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-24.5846</v>
+        <v>-58.7288</v>
       </c>
       <c r="R16" t="n">
-        <v>12.975</v>
+        <v>60.5502</v>
       </c>
       <c r="S16" t="n">
-        <v>-6.1606</v>
+        <v>10.8875</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.2607</v>
+        <v>8.0129</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.9002</v>
+        <v>2.8749</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2982000000000002</v>
+        <v>-16.2148</v>
       </c>
       <c r="W16" t="n">
-        <v>4.8313</v>
+        <v>11.901</v>
       </c>
       <c r="X16" t="n">
-        <v>-5.129300000000001</v>
+        <v>-28.1156</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. LIVINGSTON</t>
+          <t>G. FERRANDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>-38.0178</v>
+        <v>-19.0731</v>
       </c>
       <c r="E17" t="n">
-        <v>-21.1358</v>
+        <v>-20.614</v>
       </c>
       <c r="F17" t="n">
-        <v>-16.8821</v>
+        <v>1.5408</v>
       </c>
       <c r="G17" t="n">
-        <v>16.3227</v>
+        <v>-5.7651</v>
       </c>
       <c r="H17" t="n">
-        <v>-10.1091</v>
+        <v>2.0479</v>
       </c>
       <c r="I17" t="n">
-        <v>26.4318</v>
+        <v>-7.8132</v>
       </c>
       <c r="J17" t="n">
-        <v>59.7766</v>
+        <v>-0.1543999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>8.543999999999999</v>
+        <v>5.6011</v>
       </c>
       <c r="L17" t="n">
-        <v>51.2318</v>
+        <v>-5.7551</v>
       </c>
       <c r="M17" t="n">
-        <v>-43.4533</v>
+        <v>-5.6106</v>
       </c>
       <c r="N17" t="n">
-        <v>-18.6528</v>
+        <v>-3.5529</v>
       </c>
       <c r="O17" t="n">
-        <v>-24.8003</v>
+        <v>-2.0577</v>
       </c>
       <c r="P17" t="n">
-        <v>-36.4213</v>
+        <v>-11.6094</v>
       </c>
       <c r="Q17" t="n">
-        <v>-97.65390000000001</v>
+        <v>-24.5846</v>
       </c>
       <c r="R17" t="n">
-        <v>61.2331</v>
+        <v>12.975</v>
       </c>
       <c r="S17" t="n">
-        <v>-26.7107</v>
+        <v>-1.4009</v>
       </c>
       <c r="T17" t="n">
-        <v>-15.7432</v>
+        <v>-0.7066999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-10.967</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>8.790899999999999</v>
+        <v>-0.2982000000000002</v>
       </c>
       <c r="W17" t="n">
-        <v>32.4848</v>
+        <v>4.8313</v>
       </c>
       <c r="X17" t="n">
-        <v>-23.6941</v>
+        <v>-5.129300000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>-46.2968</v>
+        <v>-31.1741</v>
       </c>
       <c r="E18" t="n">
-        <v>-17.0353</v>
+        <v>-11.6561</v>
       </c>
       <c r="F18" t="n">
-        <v>-29.2612</v>
+        <v>-19.5181</v>
       </c>
       <c r="G18" t="n">
         <v>22.3085</v>
@@ -1858,13 +1858,13 @@
         <v>58.729</v>
       </c>
       <c r="S18" t="n">
-        <v>-16.3784</v>
+        <v>-1.2554</v>
       </c>
       <c r="T18" t="n">
-        <v>-3.7241</v>
+        <v>1.655</v>
       </c>
       <c r="U18" t="n">
-        <v>-12.6538</v>
+        <v>-2.9105</v>
       </c>
       <c r="V18" t="n">
         <v>-31.057</v>
@@ -1891,16 +1891,16 @@
         <v>34</v>
       </c>
       <c r="D19" t="n">
-        <v>-104.0981</v>
+        <v>-65.8124</v>
       </c>
       <c r="E19" t="n">
-        <v>-57.92849999999999</v>
+        <v>-42.59380000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-46.17</v>
+        <v>-23.2188</v>
       </c>
       <c r="G19" t="n">
-        <v>-28.406</v>
+        <v>-28.40599999999999</v>
       </c>
       <c r="H19" t="n">
         <v>-12.83700000000001</v>
@@ -1936,13 +1936,13 @@
         <v>519.0018</v>
       </c>
       <c r="S19" t="n">
-        <v>35.8107</v>
+        <v>74.09870000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>30.4638</v>
+        <v>45.7974</v>
       </c>
       <c r="U19" t="n">
-        <v>5.349099999999996</v>
+        <v>28.3022</v>
       </c>
       <c r="V19" t="n">
         <v>-81.9123</v>
